--- a/tables/extremes_associations.xlsx
+++ b/tables/extremes_associations.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,30 +372,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>predictor</t>
+          <t>Middle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Middle</t>
+          <t>Accelerated</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Accelerated</t>
+          <t>Delayed</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Delayed</t>
+          <t>Accelerated vs Middle</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Accelerated vs Middle</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Delayed vs Middle</t>
         </is>
@@ -419,30 +414,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>25197 (54.2%)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25197 (54.2%)</t>
+          <t>1311 (51.4%)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1311 (51.4%)</t>
+          <t>1420 (52.8%)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1420 (52.8%)</t>
+          <t>Chi-square, p=0.15</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.15</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -466,30 +456,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>sex</t>
+          <t>21264 (45.8%)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>21264 (45.8%)</t>
+          <t>1241 (48.6%)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1241 (48.6%)</t>
+          <t>1268 (47.2%)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1268 (47.2%)</t>
+          <t>Chi-square, p=0.15</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.15</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -513,30 +498,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>p30079</t>
+          <t>40223 (86.6%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40223 (86.6%)</t>
+          <t>2179 (85.4%)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2179 (85.4%)</t>
+          <t>2127 (79.1%)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2127 (79.1%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>Chi-square, p=7.66e-20</t>
         </is>
@@ -560,30 +540,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>p30079</t>
+          <t>82 (0.2%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82 (0.2%)</t>
+          <t>5 (0.2%)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5 (0.2%)</t>
+          <t>10 (0.4%)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10 (0.4%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>Chi-square, p=7.66e-20</t>
         </is>
@@ -607,30 +582,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>p30079</t>
+          <t>773 (1.7%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>773 (1.7%)</t>
+          <t>39 (1.5%)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>39 (1.5%)</t>
+          <t>76 (2.8%)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>76 (2.8%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>Chi-square, p=7.66e-20</t>
         </is>
@@ -654,30 +624,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>p30079</t>
+          <t>779 (1.7%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>779 (1.7%)</t>
+          <t>35 (1.4%)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>35 (1.4%)</t>
+          <t>88 (3.3%)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>88 (3.3%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>Chi-square, p=7.66e-20</t>
         </is>
@@ -701,30 +666,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>p30079</t>
+          <t>218 (0.5%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>218 (0.5%)</t>
+          <t>14 (0.5%)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14 (0.5%)</t>
+          <t>24 (0.9%)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>24 (0.9%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>Chi-square, p=7.66e-20</t>
         </is>
@@ -748,30 +708,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>p30079</t>
+          <t>248 (0.5%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>248 (0.5%)</t>
+          <t>17 (0.7%)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17 (0.7%)</t>
+          <t>32 (1.2%)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>32 (1.2%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
         <is>
           <t>Chi-square, p=7.66e-20</t>
         </is>
@@ -795,30 +750,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>smoking</t>
+          <t>25198 (54.2%)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>25198 (54.2%)</t>
+          <t>1327 (52.0%)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1327 (52.0%)</t>
+          <t>1442 (53.6%)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1442 (53.6%)</t>
+          <t>Chi-square, p=0.199</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.199</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
         <is>
           <t>Chi-square, p=0.00135</t>
         </is>
@@ -842,30 +792,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>smoking</t>
+          <t>16252 (35.0%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16252 (35.0%)</t>
+          <t>904 (35.4%)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>904 (35.4%)</t>
+          <t>883 (32.8%)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>883 (32.8%)</t>
+          <t>Chi-square, p=0.199</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.199</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
         <is>
           <t>Chi-square, p=0.00135</t>
         </is>
@@ -889,30 +834,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>smoking</t>
+          <t>4790 (10.3%)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4790 (10.3%)</t>
+          <t>309 (12.1%)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>309 (12.1%)</t>
+          <t>348 (12.9%)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>348 (12.9%)</t>
+          <t>Chi-square, p=0.199</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.199</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>Chi-square, p=0.00135</t>
         </is>
@@ -936,30 +876,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>9281 (20.0%)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9281 (20.0%)</t>
+          <t>614 (24.1%)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>614 (24.1%)</t>
+          <t>541 (20.1%)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>541 (20.1%)</t>
+          <t>Chi-square, p=5.53e-06</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
-        <is>
-          <t>Chi-square, p=5.53e-06</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -983,30 +918,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>13312 (28.7%)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13312 (28.7%)</t>
+          <t>693 (27.2%)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>693 (27.2%)</t>
+          <t>790 (29.4%)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>790 (29.4%)</t>
+          <t>Chi-square, p=5.53e-06</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
-        <is>
-          <t>Chi-square, p=5.53e-06</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1030,30 +960,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>12617 (27.2%)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12617 (27.2%)</t>
+          <t>601 (23.6%)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>601 (23.6%)</t>
+          <t>765 (28.5%)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>765 (28.5%)</t>
+          <t>Chi-square, p=5.53e-06</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
-        <is>
-          <t>Chi-square, p=5.53e-06</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1077,30 +1002,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>11251 (24.2%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11251 (24.2%)</t>
+          <t>644 (25.2%)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>644 (25.2%)</t>
+          <t>592 (22.0%)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>592 (22.0%)</t>
+          <t>Chi-square, p=5.53e-06</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
-        <is>
-          <t>Chi-square, p=5.53e-06</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1124,30 +1044,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>day_type</t>
+          <t>39878 (85.8%)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39878 (85.8%)</t>
+          <t>2188 (85.7%)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2188 (85.7%)</t>
+          <t>2283 (84.9%)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2283 (84.9%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1171,30 +1086,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>day_type</t>
+          <t>6583 (14.2%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6583 (14.2%)</t>
+          <t>364 (14.3%)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>364 (14.3%)</t>
+          <t>405 (15.1%)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>405 (15.1%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1218,30 +1128,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>fri_sun</t>
+          <t>6583 (14.2%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6583 (14.2%)</t>
+          <t>364 (14.3%)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>364 (14.3%)</t>
+          <t>405 (15.1%)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>405 (15.1%)</t>
+          <t>Chi-square, p=0.657</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.657</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1265,30 +1170,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>fri_sun</t>
+          <t>7605 (16.4%)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7605 (16.4%)</t>
+          <t>433 (17.0%)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>433 (17.0%)</t>
+          <t>428 (15.9%)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>428 (15.9%)</t>
+          <t>Chi-square, p=0.657</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.657</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1312,30 +1212,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>fri_sun</t>
+          <t>7150 (15.4%)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7150 (15.4%)</t>
+          <t>336 (13.2%)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>336 (13.2%)</t>
+          <t>454 (16.9%)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>454 (16.9%)</t>
+          <t>Chi-square, p=0.657</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.657</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1359,30 +1254,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>autumnDST</t>
+          <t>1517 (3.3%)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1517 (3.3%)</t>
+          <t>75 (2.9%)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>75 (2.9%)</t>
+          <t>94 (3.5%)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>94 (3.5%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1406,30 +1296,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>autumnDST</t>
+          <t>148 (0.3%)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>148 (0.3%)</t>
+          <t>6 (0.2%)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>6 (0.2%)</t>
+          <t>10 (0.4%)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10 (0.4%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1453,30 +1338,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>autumnDST</t>
+          <t>261 (0.6%)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>261 (0.6%)</t>
+          <t>17 (0.7%)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>17 (0.7%)</t>
+          <t>16 (0.6%)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>16 (0.6%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1500,30 +1380,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>springDST</t>
+          <t>1119 (2.4%)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1119 (2.4%)</t>
+          <t>69 (2.7%)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69 (2.7%)</t>
+          <t>61 (2.3%)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>61 (2.3%)</t>
+          <t>Chi-square, p=0.00691</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.00691</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1547,30 +1422,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>springDST</t>
+          <t>179 (0.4%)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>179 (0.4%)</t>
+          <t>24 (0.9%)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>24 (0.9%)</t>
+          <t>10 (0.4%)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>10 (0.4%)</t>
+          <t>Chi-square, p=0.00691</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.00691</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1594,30 +1464,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>springDST</t>
+          <t>272 (0.6%)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>272 (0.6%)</t>
+          <t>8 (0.3%)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>8 (0.3%)</t>
+          <t>20 (0.7%)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20 (0.7%)</t>
+          <t>Chi-square, p=0.00691</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.00691</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -1641,30 +1506,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>chrono</t>
+          <t>11086 (23.9%)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11086 (23.9%)</t>
+          <t>835 (32.7%)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>835 (32.7%)</t>
+          <t>420 (15.6%)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>420 (15.6%)</t>
+          <t>Chi-square, p=2.36e-34</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.36e-34</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
         <is>
           <t>Chi-square, p=3.38e-74</t>
         </is>
@@ -1688,30 +1548,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>chrono</t>
+          <t>14560 (31.3%)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>14560 (31.3%)</t>
+          <t>858 (33.6%)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>858 (33.6%)</t>
+          <t>624 (23.2%)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>624 (23.2%)</t>
+          <t>Chi-square, p=2.36e-34</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.36e-34</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
         <is>
           <t>Chi-square, p=3.38e-74</t>
         </is>
@@ -1735,30 +1590,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>chrono</t>
+          <t>4981 (10.7%)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4981 (10.7%)</t>
+          <t>238 (9.3%)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>238 (9.3%)</t>
+          <t>305 (11.3%)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>305 (11.3%)</t>
+          <t>Chi-square, p=2.36e-34</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.36e-34</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
         <is>
           <t>Chi-square, p=3.38e-74</t>
         </is>
@@ -1782,30 +1632,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>chrono</t>
+          <t>11862 (25.5%)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11862 (25.5%)</t>
+          <t>465 (18.2%)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>465 (18.2%)</t>
+          <t>870 (32.4%)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>870 (32.4%)</t>
+          <t>Chi-square, p=2.36e-34</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.36e-34</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
         <is>
           <t>Chi-square, p=3.38e-74</t>
         </is>
@@ -1829,30 +1674,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>chrono</t>
+          <t>3617 (7.8%)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3617 (7.8%)</t>
+          <t>117 (4.6%)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>117 (4.6%)</t>
+          <t>413 (15.4%)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>413 (15.4%)</t>
+          <t>Chi-square, p=2.36e-34</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.36e-34</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
         <is>
           <t>Chi-square, p=3.38e-74</t>
         </is>
@@ -1876,30 +1716,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>h_sleep</t>
+          <t>33855 (72.9%)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33855 (72.9%)</t>
+          <t>1724 (67.6%)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1724 (67.6%)</t>
+          <t>1886 (70.2%)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1886 (70.2%)</t>
+          <t>Chi-square, p=2.27e-06</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.27e-06</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
         <is>
           <t>Chi-square, p=0.0364</t>
         </is>
@@ -1923,30 +1758,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>h_sleep</t>
+          <t>11264 (24.2%)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11264 (24.2%)</t>
+          <t>744 (29.2%)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>744 (29.2%)</t>
+          <t>687 (25.6%)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>687 (25.6%)</t>
+          <t>Chi-square, p=2.27e-06</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.27e-06</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
         <is>
           <t>Chi-square, p=0.0364</t>
         </is>
@@ -1970,30 +1800,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>h_sleep</t>
+          <t>958 (2.1%)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>958 (2.1%)</t>
+          <t>54 (2.1%)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>54 (2.1%)</t>
+          <t>79 (2.9%)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>79 (2.9%)</t>
+          <t>Chi-square, p=2.27e-06</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.27e-06</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
         <is>
           <t>Chi-square, p=0.0364</t>
         </is>
@@ -2017,30 +1842,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>wakeup</t>
+          <t>15100 (32.5%)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>15100 (32.5%)</t>
+          <t>978 (38.3%)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>978 (38.3%)</t>
+          <t>632 (23.5%)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>632 (23.5%)</t>
+          <t>Chi-square, p=2.99e-09</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.99e-09</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
         <is>
           <t>Chi-square, p=1.89e-48</t>
         </is>
@@ -2064,30 +1884,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>wakeup</t>
+          <t>22700 (48.9%)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22700 (48.9%)</t>
+          <t>1173 (46.0%)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1173 (46.0%)</t>
+          <t>1234 (45.9%)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1234 (45.9%)</t>
+          <t>Chi-square, p=2.99e-09</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.99e-09</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
         <is>
           <t>Chi-square, p=1.89e-48</t>
         </is>
@@ -2111,30 +1926,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>wakeup</t>
+          <t>6526 (14.0%)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6526 (14.0%)</t>
+          <t>293 (11.5%)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>293 (11.5%)</t>
+          <t>563 (20.9%)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>563 (20.9%)</t>
+          <t>Chi-square, p=2.99e-09</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.99e-09</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
         <is>
           <t>Chi-square, p=1.89e-48</t>
         </is>
@@ -2158,30 +1968,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>wakeup</t>
+          <t>1827 (3.9%)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1827 (3.9%)</t>
+          <t>69 (2.7%)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69 (2.7%)</t>
+          <t>201 (7.5%)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>201 (7.5%)</t>
+          <t>Chi-square, p=2.99e-09</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
-        <is>
-          <t>Chi-square, p=2.99e-09</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
         <is>
           <t>Chi-square, p=1.89e-48</t>
         </is>
@@ -2205,30 +2010,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ever_insomnia</t>
+          <t>11087 (23.9%)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11087 (23.9%)</t>
+          <t>592 (23.2%)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>592 (23.2%)</t>
+          <t>628 (23.4%)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>628 (23.4%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -2252,30 +2052,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ever_insomnia</t>
+          <t>22053 (47.5%)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>22053 (47.5%)</t>
+          <t>1198 (46.9%)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1198 (46.9%)</t>
+          <t>1257 (46.8%)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1257 (46.8%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -2299,30 +2094,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ever_insomnia</t>
+          <t>13229 (28.5%)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13229 (28.5%)</t>
+          <t>751 (29.4%)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>751 (29.4%)</t>
+          <t>793 (29.5%)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>793 (29.5%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -2346,30 +2136,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>shift_work</t>
+          <t>20807 (44.8%)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20807 (44.8%)</t>
+          <t>1214 (47.6%)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1214 (47.6%)</t>
+          <t>1051 (39.1%)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1051 (39.1%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
         <is>
           <t>Chi-square, p=2.46e-21</t>
         </is>
@@ -2393,30 +2178,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>shift_work</t>
+          <t>1879 (4.0%)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1879 (4.0%)</t>
+          <t>108 (4.2%)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>108 (4.2%)</t>
+          <t>133 (4.9%)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>133 (4.9%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
         <is>
           <t>Chi-square, p=2.46e-21</t>
         </is>
@@ -2440,30 +2220,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>shift_work</t>
+          <t>563 (1.2%)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>563 (1.2%)</t>
+          <t>39 (1.5%)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>39 (1.5%)</t>
+          <t>40 (1.5%)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>40 (1.5%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
         <is>
           <t>Chi-square, p=2.46e-21</t>
         </is>
@@ -2487,30 +2262,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>shift_work</t>
+          <t>2019 (4.3%)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2019 (4.3%)</t>
+          <t>102 (4.0%)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>102 (4.0%)</t>
+          <t>219 (8.1%)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>219 (8.1%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
         <is>
           <t>Chi-square, p=2.46e-21</t>
         </is>
@@ -2534,30 +2304,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>night_shift</t>
+          <t>2222 (4.8%)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2222 (4.8%)</t>
+          <t>111 (4.3%)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>111 (4.3%)</t>
+          <t>141 (5.2%)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>141 (5.2%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
         <is>
           <t>Chi-square, p=2.99e-09</t>
         </is>
@@ -2581,30 +2346,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>night_shift</t>
+          <t>1312 (2.8%)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1312 (2.8%)</t>
+          <t>72 (2.8%)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>72 (2.8%)</t>
+          <t>108 (4.0%)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>108 (4.0%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
         <is>
           <t>Chi-square, p=2.99e-09</t>
         </is>
@@ -2628,30 +2388,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>night_shift</t>
+          <t>356 (0.8%)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>356 (0.8%)</t>
+          <t>25 (1.0%)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25 (1.0%)</t>
+          <t>50 (1.9%)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>50 (1.9%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
         <is>
           <t>Chi-square, p=2.99e-09</t>
         </is>
@@ -2675,30 +2430,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>night_shift</t>
+          <t>599 (1.3%)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>599 (1.3%)</t>
+          <t>41 (1.6%)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>41 (1.6%)</t>
+          <t>92 (3.4%)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>92 (3.4%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
         <is>
           <t>Chi-square, p=2.99e-09</t>
         </is>
@@ -2722,30 +2472,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>employment</t>
+          <t>23398 (50.4%)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>23398 (50.4%)</t>
+          <t>1363 (53.4%)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1363 (53.4%)</t>
+          <t>1331 (49.5%)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1331 (49.5%)</t>
+          <t>Chi-square, p=0.15</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.15</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
         <is>
           <t>Chi-square, p=5.94e-08</t>
         </is>
@@ -2769,30 +2514,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>employment</t>
+          <t>15022 (32.3%)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>15022 (32.3%)</t>
+          <t>754 (29.5%)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>754 (29.5%)</t>
+          <t>768 (28.6%)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>768 (28.6%)</t>
+          <t>Chi-square, p=0.15</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.15</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
         <is>
           <t>Chi-square, p=5.94e-08</t>
         </is>
@@ -2816,30 +2556,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>employment</t>
+          <t>1654 (3.6%)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1654 (3.6%)</t>
+          <t>112 (4.4%)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>112 (4.4%)</t>
+          <t>153 (5.7%)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>153 (5.7%)</t>
+          <t>Chi-square, p=0.15</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.15</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
         <is>
           <t>Chi-square, p=5.94e-08</t>
         </is>
@@ -2863,30 +2598,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>employment</t>
+          <t>1054 (2.3%)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1054 (2.3%)</t>
+          <t>59 (2.3%)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>59 (2.3%)</t>
+          <t>73 (2.7%)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>73 (2.7%)</t>
+          <t>Chi-square, p=0.15</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.15</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
         <is>
           <t>Chi-square, p=5.94e-08</t>
         </is>
@@ -2910,30 +2640,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>employment</t>
+          <t>136 (0.3%)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>136 (0.3%)</t>
+          <t>3 (0.1%)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>3 (0.1%)</t>
+          <t>15 (0.6%)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>15 (0.6%)</t>
+          <t>Chi-square, p=0.15</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.15</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
         <is>
           <t>Chi-square, p=5.94e-08</t>
         </is>
@@ -2957,30 +2682,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>employment</t>
+          <t>758 (1.6%)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>758 (1.6%)</t>
+          <t>35 (1.4%)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>35 (1.4%)</t>
+          <t>49 (1.8%)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>49 (1.8%)</t>
+          <t>Chi-square, p=0.15</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.15</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
         <is>
           <t>Chi-square, p=5.94e-08</t>
         </is>
@@ -3004,30 +2724,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>employment</t>
+          <t>219 (0.5%)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>219 (0.5%)</t>
+          <t>14 (0.5%)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>14 (0.5%)</t>
+          <t>16 (0.6%)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>16 (0.6%)</t>
+          <t>Chi-square, p=0.15</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
-        <is>
-          <t>Chi-square, p=0.15</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
         <is>
           <t>Chi-square, p=5.94e-08</t>
         </is>
@@ -3051,30 +2766,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>has_prescription</t>
+          <t>30877 (66.5%)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>30877 (66.5%)</t>
+          <t>1697 (66.5%)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1697 (66.5%)</t>
+          <t>1753 (65.2%)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1753 (65.2%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -3098,30 +2808,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>has_prescription</t>
+          <t>15584 (33.5%)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>15584 (33.5%)</t>
+          <t>855 (33.5%)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>855 (33.5%)</t>
+          <t>935 (34.8%)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>935 (34.8%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -3145,30 +2850,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>antihypertensive</t>
+          <t>35351 (76.1%)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>35351 (76.1%)</t>
+          <t>1961 (76.8%)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1961 (76.8%)</t>
+          <t>2043 (76.0%)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2043 (76.0%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -3192,30 +2892,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>antihypertensive</t>
+          <t>11110 (23.9%)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>11110 (23.9%)</t>
+          <t>591 (23.2%)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>591 (23.2%)</t>
+          <t>645 (24.0%)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>645 (24.0%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -3239,30 +2934,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>sleep_medication</t>
+          <t>46123 (99.3%)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>46123 (99.3%)</t>
+          <t>2529 (99.1%)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2529 (99.1%)</t>
+          <t>2658 (98.9%)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2658 (98.9%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
         <is>
           <t>Chi-square, p=0.775</t>
         </is>
@@ -3286,30 +2976,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>sleep_medication</t>
+          <t>338 (0.7%)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>338 (0.7%)</t>
+          <t>23 (0.9%)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>23 (0.9%)</t>
+          <t>30 (1.1%)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>30 (1.1%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
         <is>
           <t>Chi-square, p=0.775</t>
         </is>
@@ -3333,30 +3018,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>antidepressants</t>
+          <t>42820 (92.2%)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>42820 (92.2%)</t>
+          <t>2326 (91.1%)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2326 (91.1%)</t>
+          <t>2441 (90.8%)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2441 (90.8%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
         <is>
           <t>Chi-square, p=0.346</t>
         </is>
@@ -3380,30 +3060,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>antidepressants</t>
+          <t>3641 (7.8%)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>3641 (7.8%)</t>
+          <t>226 (8.9%)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>226 (8.9%)</t>
+          <t>247 (9.2%)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>247 (9.2%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
         <is>
           <t>Chi-square, p=0.346</t>
         </is>
@@ -3427,30 +3102,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>mood_stabiliser</t>
+          <t>46083 (99.2%)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>46083 (99.2%)</t>
+          <t>2528 (99.1%)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2528 (99.1%)</t>
+          <t>2659 (98.9%)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2659 (98.9%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -3474,30 +3144,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>mood_stabiliser</t>
+          <t>378 (0.8%)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>378 (0.8%)</t>
+          <t>24 (0.9%)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>24 (0.9%)</t>
+          <t>29 (1.1%)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>29 (1.1%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -3521,30 +3186,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>lithium</t>
+          <t>46376 (99.8%)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>46376 (99.8%)</t>
+          <t>2544 (99.7%)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2544 (99.7%)</t>
+          <t>2683 (99.8%)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2683 (99.8%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
@@ -3568,30 +3228,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>lithium</t>
+          <t>85 (0.2%)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>85 (0.2%)</t>
+          <t>8 (0.3%)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>8 (0.3%)</t>
+          <t>5 (0.2%)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>5 (0.2%)</t>
+          <t>Chi-square, p=1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
-        <is>
-          <t>Chi-square, p=1</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
         <is>
           <t>Chi-square, p=1</t>
         </is>
